--- a/Lista_Contactos.xlsx
+++ b/Lista_Contactos.xlsx
@@ -203,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Contactos" displayName="Contactos" ref="A1:J167" headerRowCount="1">
-  <autoFilter ref="A1:J167"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Contactos" displayName="Contactos" ref="A1:J169" headerRowCount="1">
+  <autoFilter ref="A1:J169"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2048,7 +2048,7 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Adriparte Gest</t>
+          <t>Addsolid</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2058,37 +2058,37 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>+351 226 158 550</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
+          <t>+351 210 103 950</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>José Luís Pereira (CEO)</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>geral@adriparte.pt</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>adriparte.pt</t>
+          <t>addsolid.com</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AFA (Grupo AFA)</t>
+          <t>Adriparte Gest</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2098,41 +2098,37 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>+351 218 981 190</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Victor de Sousa (Diretor-Geral AFA Real Estate)</t>
-        </is>
-      </c>
+          <t>+351 226 158 550</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>anaborges@afa.pt</t>
+          <t>geral@adriparte.pt</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>afa-realestate.com</t>
+          <t>adriparte.pt</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Arts Investments, SA</t>
+          <t>AFA (Grupo AFA)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2142,16 +2138,24 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>+351 291 281 182</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>+351 218 981 190</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Victor de Sousa (Diretor-Geral AFA Real Estate)</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>anaborges@afa.pt</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>artsinvestments.com</t>
+          <t>afa-realestate.com</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2168,7 +2172,7 @@
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Benoit Properties International</t>
+          <t>Arts Investments, SA</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2178,20 +2182,16 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>+44 161 250 5300 (UK)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Fredrick J. Benoit II (Director/co-fundador, 50% com Matthew Lavin)</t>
-        </is>
-      </c>
+          <t>+351 291 281 182</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>benoitproperties.com</t>
+          <t>artsinvestments.com</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Ceetrus / Nhood Portugal</t>
+          <t>Benoit Properties International</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2218,20 +2218,20 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>+351 210 537 815</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>+44 161 250 5300 (UK)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Fredrick J. Benoit II (Director/co-fundador, 50% com Matthew Lavin)</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>news@nhood.pt</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>nhood.pt</t>
+          <t>benoitproperties.com</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2241,14 +2241,14 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Coporgest</t>
+          <t>Ceetrus / Nhood Portugal</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2258,24 +2258,20 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>+351 213 108 900</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Sérgio Ferreira (fundador e CEO, homónimos sem confirmação total)</t>
-        </is>
-      </c>
+          <t>+351 210 537 815</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>geral@coporgest.com</t>
+          <t>news@nhood.pt</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>coporgest.com</t>
+          <t>nhood.pt</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2285,14 +2281,14 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>nacional</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Easyliving</t>
+          <t>Coporgest</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2302,37 +2298,41 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>+351 961 866 297</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>+351 213 108 900</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Ferreira (fundador e CEO, homónimos sem confirmação total)</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>info@easyliving.pt</t>
+          <t>geral@coporgest.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>easyliving.pt</t>
+          <t>coporgest.com</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Fercopor</t>
+          <t>Easyliving</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2342,24 +2342,20 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>+351 226 091 113</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Mário Sutil Almeida (Administrador)</t>
-        </is>
-      </c>
+          <t>+351 961 866 297</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mariosutilalmeida/</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>info@easyliving.pt</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>fercopor.pt</t>
+          <t>easyliving.pt</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2376,7 +2372,7 @@
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Fidelidade Property</t>
+          <t>Fercopor</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2386,37 +2382,41 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>+351 217 807 772</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>+351 226 091 113</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Mário Sutil Almeida (Administrador)</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>geral@fidelidadeproperty.pt</t>
-        </is>
-      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mariosutilalmeida/</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>fidelidadeproperty.pt</t>
+          <t>fercopor.pt</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FIDES – Investimentos e Gestão Imobiliária</t>
+          <t>Fidelidade Property</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>+351 213 877 749</t>
+          <t>+351 217 807 772</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -2434,10 +2434,14 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>diogopintogoncalves@imofides.com</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
+          <t>geral@fidelidadeproperty.pt</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>fidelidadeproperty.pt</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -2452,7 +2456,7 @@
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Fortera</t>
+          <t>FIDES – Investimentos e Gestão Imobiliária</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2462,41 +2466,33 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>+351 220 110 929</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
-        </is>
-      </c>
+          <t>+351 213 877 749</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>info@fortera.pt</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>fortera.pt</t>
-        </is>
-      </c>
+          <t>diogopintogoncalves@imofides.com</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Grupo Madre / Madre Imobiliário</t>
+          <t>Fortera</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2506,41 +2502,41 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>+351 213 243 220</t>
+          <t>+351 220 110 929</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Nuno Dias (Diretor Geral da Madre Imobiliário· presidente do grupo é António Parente)</t>
+          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>geral@madreimobiliario.com</t>
+          <t>info@fortera.pt</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>madreimobiliario.com</t>
+          <t>fortera.pt</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Habitat Invest</t>
+          <t>Grupo Madre / Madre Imobiliário</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2550,24 +2546,24 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>+351 213 461 024</t>
+          <t>+351 213 243 220</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Luís Corrêa de Barros (fundador e CEO)</t>
+          <t>Nuno Dias (Diretor Geral da Madre Imobiliário· presidente do grupo é António Parente)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>info@habitatinvest.pt</t>
+          <t>geral@madreimobiliario.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>habitatinvest.pt</t>
+          <t>madreimobiliario.com</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2584,7 +2580,7 @@
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>J. Dias &amp; Dias</t>
+          <t>Habitat Invest</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2594,25 +2590,29 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>+351 214 422 593</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>+351 213 461 024</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Luís Corrêa de Barros (fundador e CEO)</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>geral@jdiasdias.pt</t>
+          <t>info@habitatinvest.pt</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>jdiasdias.pt</t>
+          <t>habitatinvest.pt</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2624,7 +2624,7 @@
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Lantia</t>
+          <t>J. Dias &amp; Dias</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2634,29 +2634,25 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>+351 211 165 360</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Eduardo Kol Netto de Almeida (CEO)</t>
-        </is>
-      </c>
+          <t>+351 214 422 593</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>geral@lantia.pt</t>
+          <t>geral@jdiasdias.pt</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>lantia.pt</t>
+          <t>jdiasdias.pt</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -2668,7 +2664,7 @@
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Libertas – Investimentos Imobiliários</t>
+          <t>Lantia</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2678,24 +2674,24 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>+351 213 243 050</t>
+          <t>+351 211 165 360</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>António Gonçalves (Fundador)</t>
+          <t>Eduardo Kol Netto de Almeida (CEO)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>libertas@libertas.pt</t>
+          <t>geral@lantia.pt</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>libertas.pt</t>
+          <t>lantia.pt</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2712,7 +2708,7 @@
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Mesmo Valor (Mesmovalor, S.A.)</t>
+          <t>Libertas – Investimentos Imobiliários</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2722,41 +2718,41 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>+351 223 274 626</t>
+          <t>+351 213 243 050</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Pedro Teixeira Paredes (CEO)</t>
+          <t>António Gonçalves (Fundador)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>geral@mesmovalor.pt</t>
+          <t>libertas@libertas.pt</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>mesmovalor.pt</t>
+          <t>libertas.pt</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Névoa, S.A.</t>
+          <t>Mesmo Valor (Mesmovalor, S.A.)</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2766,33 +2762,41 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>+351 253 240 010</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>+351 223 274 626</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Teixeira Paredes (CEO)</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>geral@mesmovalor.pt</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>nevoa.pt</t>
+          <t>mesmovalor.pt</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Névoa, S.A.</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2802,24 +2806,16 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>+351 915 896 265</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Federico Rosales (cofundador e CEO)</t>
-        </is>
-      </c>
+          <t>+351 253 240 010</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>info@primelisbon.com</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>primelisbon.com</t>
+          <t>nevoa.pt</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2836,7 +2832,7 @@
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Qualive</t>
+          <t>Prime Portugal</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2846,29 +2842,41 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>+351 226 090 545</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>+351 915 896 265</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Federico Rosales (cofundador e CEO)</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>info@primelisbon.com</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>primelisbon.com</t>
+        </is>
+      </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Rio Capital / Grupo Rio</t>
+          <t>Qualive</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2878,37 +2886,29 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>+351 213 861 065</t>
+          <t>+351 226 090 545</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>geral@riocapital.pt</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>riocapital.pt</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>Rio Capital / Grupo Rio</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2918,20 +2918,20 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>+351 213 303 727</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
-        </is>
-      </c>
+          <t>+351 213 861 065</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>geral@riocapital.pt</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>roundhillcapital.com</t>
+          <t>riocapital.pt</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2948,7 +2948,7 @@
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Screendomus (Grupo Teixeira)</t>
+          <t>Round Hill Capital</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2958,24 +2958,20 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>+351 928 110 064</t>
+          <t>+351 213 303 727</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>geral@screendomus.com</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>screendomus.com</t>
+          <t>roundhillcapital.com</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2992,7 +2988,7 @@
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Stone Capital</t>
+          <t>Screendomus (Grupo Teixeira)</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3002,24 +2998,24 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>+351 210 416 350</t>
+          <t>+351 928 110 064</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Geoffroy Moreno (Co-Founder)</t>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>info@stonecapital.pt</t>
+          <t>geral@screendomus.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>stonecapital.pt</t>
+          <t>screendomus.com</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3036,7 +3032,7 @@
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Teixeira Duarte Real Estate</t>
+          <t>Stone Capital</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3046,25 +3042,29 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>+351 217 912 300</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>+351 210 416 350</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Geoffroy Moreno (Co-Founder)</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>info@tdimobiliaria.pt</t>
+          <t>info@stonecapital.pt</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>tdimobiliaria.pt</t>
+          <t>stonecapital.pt</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3076,7 +3076,7 @@
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>YARD Properties</t>
+          <t>Teixeira Duarte Real Estate</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3086,29 +3086,25 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>+351 918 888 353</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>David Rabbi (fundador)</t>
-        </is>
-      </c>
+          <t>+351 217 912 300</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>sales@355outubro.com</t>
+          <t>info@tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>yardproperties.pt</t>
+          <t>tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3120,55 +3116,51 @@
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>YARD Properties</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>900 264 096 (ES)</t>
+          <t>+351 918 888 353</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
+          <t>David Rabbi (fundador)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>info@aedashomes.com</t>
+          <t>sales@355outubro.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>ribamarportimao.com</t>
+          <t>yardproperties.pt</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Antrix</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -3178,33 +3170,33 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
+          <t>900 264 096 (ES)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>info@antrix.pt</t>
+          <t>info@aedashomes.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>antrix.pt</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3216,7 +3208,7 @@
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Arish Capital Partners</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3226,41 +3218,45 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>info@antrix.pt</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>arishcapitalpartners.com</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>Grândola</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -3270,45 +3266,41 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (CEO)</t>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>info@carvoeirobranco.com</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3318,45 +3310,45 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
+          <t>Erik de Vlieger (CEO)</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -3366,45 +3358,45 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 461 462</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
+          <t>Paulo Castro (CEO)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>geral@castro-group.pt</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3414,41 +3406,45 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
+          <t>+351 234 480 570</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
+          <t>Artur Varum (CEO)</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>info@civilria.pt</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3458,41 +3454,41 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
+          <t>+351 253 089 932</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
+          <t>Diogo Baptista Antunes (CEO)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3502,45 +3498,41 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
+          <t>+351 289 381 550</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
+          <t>Reinaldo Teixeira (Administrador)</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>aca@grupo-aca.com</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -3550,33 +3542,33 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Vila Nova de Famalicão</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -3588,7 +3580,7 @@
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -3598,41 +3590,45 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>+351 253 105 331</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
+          <t>Domingos Correia (CEO)</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>geral@arliz.co</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -3642,45 +3638,41 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 913 470 147</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
+          <t>Miguel Tilli (fundador e CEO)</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>info@pinehill.pt</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3690,45 +3682,45 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
+          <t>Nuno Pinheiro (fundador)</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>info@quintadolago.com</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -3738,41 +3730,45 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
+          <t>+351 289 390 700</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+          <t>Sean Moriarty (CEO)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -3782,41 +3778,41 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
+          <t>+351 219 362 960</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>casais@casais.pt</t>
-        </is>
-      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DST Real Estate (Grupo dst)</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -3826,20 +3822,24 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>+351 253 307 200</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>+351 253 305 490</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>geral@dstsgps.com</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>dstsgps.com</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>DST Real Estate (Grupo dst)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -3866,41 +3866,37 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
+          <t>+351 253 307 200</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>geral@garcia.pt</t>
+          <t>geral@dstsgps.com</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>dstsgps.com</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -3910,41 +3906,41 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -3954,37 +3950,41 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
+          <t>+351 253 685 109</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>acrescentar@grupoacrescentar.pt</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Hievila – Empreendimentos Imobiliários</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -3994,37 +3994,37 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>+351 239 091 692</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
+          <t>273 332 784 (confirmar)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>hievila@hievila.com</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>hievila.com</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>iLanga Capital (Ohai Resorts)</t>
+          <t>Hievila – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4034,41 +4034,37 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>+351 262 561 800</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Pelayo Cortina Koplowitz (fundador)</t>
-        </is>
-      </c>
+          <t>+351 239 091 692</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>info.nazare@ohairesorts.com</t>
+          <t>hievila@hievila.com</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>ohairesorts.com</t>
+          <t>hievila.com</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Nazaré</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>iLanga Capital (Ohai Resorts)</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4078,41 +4074,41 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
+          <t>+351 262 561 800</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
+          <t>Pelayo Cortina Koplowitz (fundador)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>geral@jhomea.pt</t>
+          <t>info.nazare@ohairesorts.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>ohairesorts.com</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Nazaré</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4122,37 +4118,41 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
+          <t>+351 934 175 642</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>José Miguel Afonso (CEO/fundador)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -4162,37 +4162,37 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>rgodinho@royalprime.pt</t>
-        </is>
-      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -4202,37 +4202,37 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Castelo Branco</t>
         </is>
       </c>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -4242,41 +4242,37 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
+          <t>+351 939 443 765</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -4286,77 +4282,81 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
+          <t>+351 255 433 572</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
+          <t>tps.com.pt</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
           <t>vomera.pt</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>Santarém</t>
         </is>
       </c>
-      <c r="J85" s="4" t="inlineStr">
+      <c r="J86" s="4" t="inlineStr">
         <is>
           <t>Santarém</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Alecrim Real Estate (Lince Capital)</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr"/>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr"/>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>lince-capital.com</t>
-        </is>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="J86" s="8" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Alecrim Real Estate (Lince Capital)</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -4367,23 +4367,19 @@
       <c r="C87" s="8" t="inlineStr"/>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Fernando Vasco Costa (CEO)</t>
+          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="G87" s="6" t="inlineStr"/>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>lince-capital.com</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -4400,7 +4396,7 @@
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>VIZTA (ex-Nexity Portugal)</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -4411,40 +4407,40 @@
       <c r="C88" s="8" t="inlineStr"/>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
+          <t>Fernando Vasco Costa (CEO)</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/tamir-luria/</t>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>info@ancora-inv.com</t>
+          <t>privacidade@vizta.pt</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>ancora-inv.com</t>
+          <t>vizta.pt</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
+          <t>Âncora Investments</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -4455,13 +4451,25 @@
       <c r="C89" s="8" t="inlineStr"/>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr"/>
+          <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tamir-luria/</t>
+        </is>
+      </c>
       <c r="F89" s="6" t="inlineStr"/>
-      <c r="G89" s="6" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>info@ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>ancora-inv.com</t>
+        </is>
+      </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Porto</t>
@@ -4476,7 +4484,7 @@
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Fungepi (Grupo Novo Banco)</t>
+          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -4485,26 +4493,30 @@
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr"/>
-      <c r="D90" s="6" t="inlineStr"/>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
+        </is>
+      </c>
       <c r="E90" s="6" t="inlineStr"/>
       <c r="F90" s="6" t="inlineStr"/>
       <c r="G90" s="6" t="inlineStr"/>
       <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Frederico Ressano (promotor individual)</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -4515,7 +4527,7 @@
       <c r="C91" s="8" t="inlineStr"/>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
+          <t>Frederico Ressano</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr"/>
@@ -4523,12 +4535,12 @@
       <c r="G91" s="6" t="inlineStr"/>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>hines.com</t>
+          <t>theparkcascaisresidences.com</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr">
@@ -4540,7 +4552,7 @@
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Fungepi (Grupo Novo Banco)</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -4549,34 +4561,26 @@
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr"/>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
-        </is>
-      </c>
+      <c r="D92" s="6" t="inlineStr"/>
       <c r="E92" s="6" t="inlineStr"/>
       <c r="F92" s="6" t="inlineStr"/>
       <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>imolote.pt</t>
-        </is>
-      </c>
+      <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -4587,28 +4591,32 @@
       <c r="C93" s="8" t="inlineStr"/>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr"/>
       <c r="F93" s="6" t="inlineStr"/>
       <c r="G93" s="6" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>hines.com</t>
+        </is>
+      </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>KKR Imo, S.A.</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -4619,28 +4627,32 @@
       <c r="C94" s="8" t="inlineStr"/>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr"/>
       <c r="F94" s="6" t="inlineStr"/>
       <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Neptune Developments</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -4649,30 +4661,30 @@
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr"/>
-      <c r="D95" s="6" t="inlineStr"/>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+        </is>
+      </c>
       <c r="E95" s="6" t="inlineStr"/>
       <c r="F95" s="6" t="inlineStr"/>
       <c r="G95" s="6" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>neptune-developments.com</t>
-        </is>
-      </c>
+      <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Onyria Group</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -4683,20 +4695,16 @@
       <c r="C96" s="8" t="inlineStr"/>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
       <c r="F96" s="6" t="inlineStr"/>
       <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>onyriagroup.com</t>
-        </is>
-      </c>
+      <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
@@ -4708,7 +4716,7 @@
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Neptune Developments</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -4717,30 +4725,30 @@
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Nuno Cunha (Managing Director)</t>
-        </is>
-      </c>
+      <c r="D97" s="6" t="inlineStr"/>
       <c r="E97" s="6" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr"/>
       <c r="G97" s="6" t="inlineStr"/>
-      <c r="H97" s="6" t="inlineStr"/>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>neptune-developments.com</t>
+        </is>
+      </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>REABILITA</t>
+          <t>Onyria Group</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -4749,18 +4757,22 @@
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr"/>
-      <c r="D98" s="6" t="inlineStr"/>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+        </is>
+      </c>
       <c r="E98" s="6" t="inlineStr"/>
       <c r="F98" s="6" t="inlineStr"/>
       <c r="G98" s="6" t="inlineStr"/>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>reabilita.pt</t>
+          <t>onyriagroup.com</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
@@ -4772,7 +4784,7 @@
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -4781,26 +4793,30 @@
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr"/>
-      <c r="D99" s="6" t="inlineStr"/>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Nuno Cunha (Managing Director)</t>
+        </is>
+      </c>
       <c r="E99" s="6" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr"/>
       <c r="G99" s="6" t="inlineStr"/>
       <c r="H99" s="6" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REABILITA</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -4813,22 +4829,26 @@
       <c r="E100" s="6" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr"/>
       <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>reabilita.pt</t>
+        </is>
+      </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -4841,14 +4861,10 @@
       <c r="E101" s="6" t="inlineStr"/>
       <c r="F101" s="6" t="inlineStr"/>
       <c r="G101" s="6" t="inlineStr"/>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>altadelisboa.com</t>
-        </is>
-      </c>
+      <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -4860,7 +4876,7 @@
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -4869,22 +4885,14 @@
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr"/>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
-        </is>
-      </c>
+      <c r="D102" s="6" t="inlineStr"/>
       <c r="E102" s="6" t="inlineStr"/>
       <c r="F102" s="6" t="inlineStr"/>
       <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>shaluinvest.pt</t>
-        </is>
-      </c>
+      <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
@@ -4896,7 +4904,7 @@
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -4909,94 +4917,90 @@
       <c r="E103" s="6" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr"/>
       <c r="G103" s="6" t="inlineStr"/>
-      <c r="H103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>altadelisboa.com</t>
+        </is>
+      </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>Shalu Investments</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr"/>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
-        </is>
-      </c>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr"/>
       <c r="F104" s="6" t="inlineStr"/>
       <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Grândola/Lagoa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Emblezart</t>
-        </is>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>Taga Urbanic</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr"/>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+      <c r="D105" s="6" t="inlineStr"/>
+      <c r="E105" s="6" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr"/>
       <c r="G105" s="6" t="inlineStr"/>
       <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -5007,12 +5011,12 @@
       <c r="C106" s="8" t="inlineStr"/>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -5020,7 +5024,7 @@
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
@@ -5032,7 +5036,7 @@
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -5043,36 +5047,32 @@
       <c r="C107" s="8" t="inlineStr"/>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Igor Castro (CEO)</t>
+          <t>David Faria (CEO e sócio único)</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
       <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="H107" s="6" t="inlineStr"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
@@ -5083,36 +5083,32 @@
       <c r="C108" s="8" t="inlineStr"/>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
+          <t>Carlos Silva Neves (administrador)</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
       <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -5123,36 +5119,36 @@
       <c r="C109" s="8" t="inlineStr"/>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+          <t>Igor Castro (CEO)</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
       <c r="G109" s="6" t="inlineStr"/>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>ombria.com</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
@@ -5163,24 +5159,24 @@
       <c r="C110" s="8" t="inlineStr"/>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
+          <t>António Ribeiro da Cunha (CEO)</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
       <c r="G110" s="6" t="inlineStr"/>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>soccal-vaz.com</t>
+          <t>mellordc.pt</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
@@ -5192,7 +5188,7 @@
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -5203,36 +5199,36 @@
       <c r="C111" s="8" t="inlineStr"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
       <c r="G111" s="6" t="inlineStr"/>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>ombria.com</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
@@ -5243,36 +5239,36 @@
       <c r="C112" s="8" t="inlineStr"/>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
+          <t>António Vaz (fundador e CEO)</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
       <c r="G112" s="6" t="inlineStr"/>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>soccal-vaz.com</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -5283,36 +5279,36 @@
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
+          <t>Alain Gross (Co-Founder e CEO)</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
       <c r="G113" s="6" t="inlineStr"/>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>Algarve Property Shops</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
@@ -5321,26 +5317,38 @@
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr"/>
-      <c r="D114" s="6" t="inlineStr"/>
-      <c r="E114" s="6" t="inlineStr"/>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+        </is>
+      </c>
       <c r="F114" s="6" t="inlineStr"/>
       <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>sonaesierra.com</t>
+        </is>
+      </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>nacional</t>
         </is>
       </c>
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -5349,26 +5357,38 @@
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr"/>
-      <c r="D115" s="6" t="inlineStr"/>
-      <c r="E115" s="6" t="inlineStr"/>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+        </is>
+      </c>
       <c r="F115" s="6" t="inlineStr"/>
       <c r="G115" s="6" t="inlineStr"/>
-      <c r="H115" s="6" t="inlineStr"/>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -5377,18 +5397,14 @@
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr"/>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
+      <c r="D116" s="6" t="inlineStr"/>
       <c r="E116" s="6" t="inlineStr"/>
       <c r="F116" s="6" t="inlineStr"/>
       <c r="G116" s="6" t="inlineStr"/>
       <c r="H116" s="6" t="inlineStr"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -5400,7 +5416,7 @@
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -5409,22 +5425,14 @@
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr"/>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
+      <c r="D117" s="6" t="inlineStr"/>
       <c r="E117" s="6" t="inlineStr"/>
       <c r="F117" s="6" t="inlineStr"/>
       <c r="G117" s="6" t="inlineStr"/>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
@@ -5436,7 +5444,7 @@
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
@@ -5445,26 +5453,30 @@
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr"/>
-      <c r="D118" s="6" t="inlineStr"/>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="E118" s="6" t="inlineStr"/>
       <c r="F118" s="6" t="inlineStr"/>
       <c r="G118" s="6" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
@@ -5473,26 +5485,34 @@
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr"/>
-      <c r="D119" s="6" t="inlineStr"/>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="E119" s="6" t="inlineStr"/>
       <c r="F119" s="6" t="inlineStr"/>
       <c r="G119" s="6" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr"/>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
@@ -5505,26 +5525,22 @@
       <c r="E120" s="6" t="inlineStr"/>
       <c r="F120" s="6" t="inlineStr"/>
       <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
@@ -5540,7 +5556,7 @@
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -5552,7 +5568,7 @@
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
@@ -5565,22 +5581,26 @@
       <c r="E122" s="6" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr"/>
       <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
@@ -5593,26 +5613,22 @@
       <c r="E123" s="6" t="inlineStr"/>
       <c r="F123" s="6" t="inlineStr"/>
       <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
@@ -5628,19 +5644,19 @@
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Guarda</t>
         </is>
       </c>
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
@@ -5649,30 +5665,30 @@
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr"/>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+      <c r="D125" s="6" t="inlineStr"/>
       <c r="E125" s="6" t="inlineStr"/>
       <c r="F125" s="6" t="inlineStr"/>
       <c r="G125" s="6" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
@@ -5681,30 +5697,26 @@
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr"/>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
+      <c r="D126" s="6" t="inlineStr"/>
       <c r="E126" s="6" t="inlineStr"/>
       <c r="F126" s="6" t="inlineStr"/>
       <c r="G126" s="6" t="inlineStr"/>
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
@@ -5715,32 +5727,28 @@
       <c r="C127" s="8" t="inlineStr"/>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr"/>
       <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
@@ -5751,7 +5759,7 @@
       <c r="C128" s="8" t="inlineStr"/>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr"/>
@@ -5760,19 +5768,19 @@
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
@@ -5781,26 +5789,34 @@
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr"/>
-      <c r="D129" s="6" t="inlineStr"/>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="E129" s="6" t="inlineStr"/>
       <c r="F129" s="6" t="inlineStr"/>
       <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
@@ -5809,26 +5825,30 @@
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr"/>
-      <c r="D130" s="6" t="inlineStr"/>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="E130" s="6" t="inlineStr"/>
       <c r="F130" s="6" t="inlineStr"/>
       <c r="G130" s="6" t="inlineStr"/>
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
@@ -5844,7 +5864,7 @@
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
@@ -5856,7 +5876,7 @@
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
@@ -5869,26 +5889,22 @@
       <c r="E132" s="6" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr"/>
       <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
@@ -5897,22 +5913,14 @@
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr"/>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+      <c r="D133" s="6" t="inlineStr"/>
       <c r="E133" s="6" t="inlineStr"/>
       <c r="F133" s="6" t="inlineStr"/>
       <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
@@ -5924,7 +5932,7 @@
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
@@ -5939,24 +5947,24 @@
       <c r="G134" s="6" t="inlineStr"/>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -5965,26 +5973,34 @@
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr"/>
-      <c r="D135" s="6" t="inlineStr"/>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="E135" s="6" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr"/>
       <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
@@ -5993,26 +6009,30 @@
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr"/>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+      <c r="D136" s="6" t="inlineStr"/>
       <c r="E136" s="6" t="inlineStr"/>
       <c r="F136" s="6" t="inlineStr"/>
       <c r="G136" s="6" t="inlineStr"/>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="inlineStr"/>
-      <c r="J136" s="8" t="inlineStr"/>
+          <t>glowing.pt</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="J136" s="8" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
@@ -6021,34 +6041,26 @@
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr"/>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+      <c r="D137" s="6" t="inlineStr"/>
       <c r="E137" s="6" t="inlineStr"/>
       <c r="F137" s="6" t="inlineStr"/>
       <c r="G137" s="6" t="inlineStr"/>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
+      <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -6059,28 +6071,24 @@
       <c r="C138" s="8" t="inlineStr"/>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
       <c r="F138" s="6" t="inlineStr"/>
       <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr"/>
-      <c r="I138" s="8" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="J138" s="8" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="inlineStr"/>
+      <c r="J138" s="8" t="inlineStr"/>
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
@@ -6089,30 +6097,34 @@
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr"/>
-      <c r="D139" s="6" t="inlineStr"/>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
       <c r="E139" s="6" t="inlineStr"/>
       <c r="F139" s="6" t="inlineStr"/>
       <c r="G139" s="6" t="inlineStr"/>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>grupomaisempresas.pt</t>
+          <t>andrejordangroup.pt</t>
         </is>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -6123,32 +6135,28 @@
       <c r="C140" s="8" t="inlineStr"/>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Ioav Blanche (presidente)</t>
+          <t>Aníbal Cristina (fundador, 1990)</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr"/>
       <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>gruponbportugal.pt</t>
-        </is>
-      </c>
+      <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
@@ -6157,34 +6165,30 @@
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr"/>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
-        </is>
-      </c>
+      <c r="D141" s="6" t="inlineStr"/>
       <c r="E141" s="6" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr"/>
       <c r="G141" s="6" t="inlineStr"/>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
@@ -6193,18 +6197,22 @@
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr"/>
-      <c r="D142" s="6" t="inlineStr"/>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="E142" s="6" t="inlineStr"/>
       <c r="F142" s="6" t="inlineStr"/>
       <c r="G142" s="6" t="inlineStr"/>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr">
@@ -6216,7 +6224,7 @@
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
@@ -6225,30 +6233,34 @@
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr"/>
-      <c r="D143" s="6" t="inlineStr"/>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="E143" s="6" t="inlineStr"/>
       <c r="F143" s="6" t="inlineStr"/>
       <c r="G143" s="6" t="inlineStr"/>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
@@ -6261,22 +6273,26 @@
       <c r="E144" s="6" t="inlineStr"/>
       <c r="F144" s="6" t="inlineStr"/>
       <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>hillside.pt</t>
+        </is>
+      </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -6291,12 +6307,12 @@
       <c r="G145" s="6" t="inlineStr"/>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>leparc.pt</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="J145" s="8" t="inlineStr">
@@ -6308,7 +6324,7 @@
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
@@ -6317,34 +6333,26 @@
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr"/>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
+      <c r="D146" s="6" t="inlineStr"/>
       <c r="E146" s="6" t="inlineStr"/>
       <c r="F146" s="6" t="inlineStr"/>
       <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>luxpremium.net</t>
-        </is>
-      </c>
+      <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -6353,18 +6361,18 @@
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr"/>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
+      <c r="D147" s="6" t="inlineStr"/>
       <c r="E147" s="6" t="inlineStr"/>
       <c r="F147" s="6" t="inlineStr"/>
       <c r="G147" s="6" t="inlineStr"/>
-      <c r="H147" s="6" t="inlineStr"/>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J147" s="8" t="inlineStr">
@@ -6376,7 +6384,7 @@
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
@@ -6385,26 +6393,34 @@
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr"/>
-      <c r="D148" s="6" t="inlineStr"/>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="E148" s="6" t="inlineStr"/>
       <c r="F148" s="6" t="inlineStr"/>
       <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -6415,32 +6431,28 @@
       <c r="C149" s="8" t="inlineStr"/>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr"/>
       <c r="F149" s="6" t="inlineStr"/>
       <c r="G149" s="6" t="inlineStr"/>
-      <c r="H149" s="6" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -6456,19 +6468,19 @@
       <c r="H150" s="6" t="inlineStr"/>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Santarém</t>
         </is>
       </c>
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -6479,28 +6491,32 @@
       <c r="C151" s="8" t="inlineStr"/>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
+          <t>Yehonatan Gourvitch (CEO)</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr"/>
       <c r="F151" s="6" t="inlineStr"/>
       <c r="G151" s="6" t="inlineStr"/>
-      <c r="H151" s="6" t="inlineStr"/>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
@@ -6513,14 +6529,10 @@
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="6" t="inlineStr"/>
       <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="H152" s="6" t="inlineStr"/>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr">
@@ -6532,7 +6544,7 @@
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -6541,26 +6553,30 @@
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr"/>
-      <c r="D153" s="6" t="inlineStr"/>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
       <c r="E153" s="6" t="inlineStr"/>
       <c r="F153" s="6" t="inlineStr"/>
       <c r="G153" s="6" t="inlineStr"/>
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
     </row>
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
@@ -6569,30 +6585,30 @@
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr"/>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
+      <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="6" t="inlineStr"/>
       <c r="F154" s="6" t="inlineStr"/>
       <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -6608,19 +6624,19 @@
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -6629,14 +6645,18 @@
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr"/>
-      <c r="D156" s="6" t="inlineStr"/>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="E156" s="6" t="inlineStr"/>
       <c r="F156" s="6" t="inlineStr"/>
       <c r="G156" s="6" t="inlineStr"/>
       <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr">
@@ -6648,7 +6668,7 @@
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -6657,30 +6677,26 @@
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr"/>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+      <c r="D157" s="6" t="inlineStr"/>
       <c r="E157" s="6" t="inlineStr"/>
       <c r="F157" s="6" t="inlineStr"/>
       <c r="G157" s="6" t="inlineStr"/>
       <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -6689,34 +6705,26 @@
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr"/>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+      <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="6" t="inlineStr"/>
       <c r="F158" s="6" t="inlineStr"/>
       <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
@@ -6725,26 +6733,30 @@
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr"/>
-      <c r="D159" s="6" t="inlineStr"/>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
       <c r="E159" s="6" t="inlineStr"/>
       <c r="F159" s="6" t="inlineStr"/>
       <c r="G159" s="6" t="inlineStr"/>
       <c r="H159" s="6" t="inlineStr"/>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -6753,30 +6765,34 @@
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr"/>
-      <c r="D160" s="6" t="inlineStr"/>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
       <c r="E160" s="6" t="inlineStr"/>
       <c r="F160" s="6" t="inlineStr"/>
       <c r="G160" s="6" t="inlineStr"/>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>southshoreinvest.com</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -6792,19 +6808,19 @@
       <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -6819,24 +6835,24 @@
       <c r="G162" s="6" t="inlineStr"/>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>valentavillas.com</t>
+          <t>southshoreinvest.com</t>
         </is>
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="163" ht="26" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -6852,19 +6868,19 @@
       <c r="H163" s="6" t="inlineStr"/>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -6873,34 +6889,30 @@
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr"/>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+      <c r="D164" s="6" t="inlineStr"/>
       <c r="E164" s="6" t="inlineStr"/>
       <c r="F164" s="6" t="inlineStr"/>
       <c r="G164" s="6" t="inlineStr"/>
       <c r="H164" s="6" t="inlineStr">
         <is>
-          <t>ugp.ie</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>Urban Office</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -6913,26 +6925,22 @@
       <c r="E165" s="6" t="inlineStr"/>
       <c r="F165" s="6" t="inlineStr"/>
       <c r="G165" s="6" t="inlineStr"/>
-      <c r="H165" s="6" t="inlineStr">
-        <is>
-          <t>urbanoffice.pt</t>
-        </is>
-      </c>
+      <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>Torres Vedras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -6941,18 +6949,22 @@
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr"/>
-      <c r="D166" s="6" t="inlineStr"/>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="E166" s="6" t="inlineStr"/>
       <c r="F166" s="6" t="inlineStr"/>
       <c r="G166" s="6" t="inlineStr"/>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>valedolobo.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
@@ -6964,7 +6976,7 @@
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Office</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -6979,15 +6991,79 @@
       <c r="G167" s="6" t="inlineStr"/>
       <c r="H167" s="6" t="inlineStr">
         <is>
+          <t>urbanoffice.pt</t>
+        </is>
+      </c>
+      <c r="I167" s="8" t="inlineStr">
+        <is>
+          <t>Torres Vedras</t>
+        </is>
+      </c>
+      <c r="J167" s="8" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="26" customHeight="1">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr"/>
+      <c r="D168" s="6" t="inlineStr"/>
+      <c r="E168" s="6" t="inlineStr"/>
+      <c r="F168" s="6" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr"/>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="I168" s="8" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="J168" s="8" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="26" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr"/>
+      <c r="D169" s="6" t="inlineStr"/>
+      <c r="E169" s="6" t="inlineStr"/>
+      <c r="F169" s="6" t="inlineStr"/>
+      <c r="G169" s="6" t="inlineStr"/>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
           <t>vilagale.com</t>
         </is>
       </c>
-      <c r="I167" s="8" t="inlineStr">
+      <c r="I169" s="8" t="inlineStr">
         <is>
           <t>Golegã</t>
         </is>
       </c>
-      <c r="J167" s="8" t="inlineStr">
+      <c r="J169" s="8" t="inlineStr">
         <is>
           <t>Santarém</t>
         </is>
@@ -7026,34 +7102,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -7094,7 +7170,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
@@ -7104,7 +7180,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -7114,7 +7190,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -7124,7 +7200,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6">
@@ -7154,7 +7230,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">

--- a/Lista_Contactos.xlsx
+++ b/Lista_Contactos.xlsx
@@ -203,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Contactos" displayName="Contactos" ref="A1:J169" headerRowCount="1">
-  <autoFilter ref="A1:J169"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Contactos" displayName="Contactos" ref="A1:J172" headerRowCount="1">
+  <autoFilter ref="A1:J172"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4316,7 +4316,7 @@
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>Violas Ferreira (Grupo HVF)</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -4326,77 +4326,81 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
+          <t>+351 227 340 823</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+          <t>Tiago Violas Ferreira (líder do grupo)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>info@violasferreira.com</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
+          <t>violasferreira.com</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Espinho</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
           <t>vomera.pt</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>Santarém</t>
         </is>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>Santarém</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Alecrim Real Estate (Lince Capital)</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr"/>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr"/>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>lince-capital.com</t>
-        </is>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Alecrim Real Estate (Lince Capital)</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -4407,23 +4411,19 @@
       <c r="C88" s="8" t="inlineStr"/>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Fernando Vasco Costa (CEO)</t>
+          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="G88" s="6" t="inlineStr"/>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>lince-capital.com</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -4440,7 +4440,7 @@
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>VIZTA (ex-Nexity Portugal)</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -4451,40 +4451,40 @@
       <c r="C89" s="8" t="inlineStr"/>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
+          <t>Fernando Vasco Costa (CEO)</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/tamir-luria/</t>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>info@ancora-inv.com</t>
+          <t>privacidade@vizta.pt</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>ancora-inv.com</t>
+          <t>vizta.pt</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
+          <t>Âncora Investments</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -4495,13 +4495,25 @@
       <c r="C90" s="8" t="inlineStr"/>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr"/>
+          <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tamir-luria/</t>
+        </is>
+      </c>
       <c r="F90" s="6" t="inlineStr"/>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>info@ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>ancora-inv.com</t>
+        </is>
+      </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Porto</t>
@@ -4516,7 +4528,7 @@
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Frederico Ressano (promotor individual)</t>
+          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -4527,32 +4539,28 @@
       <c r="C91" s="8" t="inlineStr"/>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Frederico Ressano</t>
+          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr"/>
       <c r="F91" s="6" t="inlineStr"/>
       <c r="G91" s="6" t="inlineStr"/>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>theparkcascaisresidences.com</t>
-        </is>
-      </c>
+      <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Fungepi (Grupo Novo Banco)</t>
+          <t>Frederico Ressano (promotor individual)</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -4561,14 +4569,22 @@
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr"/>
-      <c r="D92" s="6" t="inlineStr"/>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Frederico Ressano</t>
+        </is>
+      </c>
       <c r="E92" s="6" t="inlineStr"/>
       <c r="F92" s="6" t="inlineStr"/>
       <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>theparkcascaisresidences.com</t>
+        </is>
+      </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
@@ -4580,7 +4596,7 @@
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Fungepi (Grupo Novo Banco)</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -4589,19 +4605,11 @@
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr"/>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
-        </is>
-      </c>
+      <c r="D93" s="6" t="inlineStr"/>
       <c r="E93" s="6" t="inlineStr"/>
       <c r="F93" s="6" t="inlineStr"/>
       <c r="G93" s="6" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>hines.com</t>
-        </is>
-      </c>
+      <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" s="8" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -4616,7 +4624,7 @@
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -4627,7 +4635,7 @@
       <c r="C94" s="8" t="inlineStr"/>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr"/>
@@ -4635,24 +4643,24 @@
       <c r="G94" s="6" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>imolote.pt</t>
+          <t>hines.com</t>
         </is>
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -4663,13 +4671,17 @@
       <c r="C95" s="8" t="inlineStr"/>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr"/>
       <c r="F95" s="6" t="inlineStr"/>
       <c r="G95" s="6" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Porto</t>
@@ -4684,7 +4696,7 @@
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>KKR Imo, S.A.</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -4695,7 +4707,7 @@
       <c r="C96" s="8" t="inlineStr"/>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
@@ -4704,19 +4716,19 @@
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Neptune Developments</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -4725,18 +4737,18 @@
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
-      <c r="D97" s="6" t="inlineStr"/>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+        </is>
+      </c>
       <c r="E97" s="6" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr"/>
       <c r="G97" s="6" t="inlineStr"/>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>neptune-developments.com</t>
-        </is>
-      </c>
+      <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
@@ -4748,7 +4760,7 @@
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Onyria Group</t>
+          <t>Neptune Developments</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -4757,17 +4769,13 @@
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr"/>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
-        </is>
-      </c>
+      <c r="D98" s="6" t="inlineStr"/>
       <c r="E98" s="6" t="inlineStr"/>
       <c r="F98" s="6" t="inlineStr"/>
       <c r="G98" s="6" t="inlineStr"/>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>onyriagroup.com</t>
+          <t>neptune-developments.com</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -4784,7 +4792,7 @@
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Onyria Group</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -4795,28 +4803,32 @@
       <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Nuno Cunha (Managing Director)</t>
+          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr"/>
       <c r="G99" s="6" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>onyriagroup.com</t>
+        </is>
+      </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>REABILITA</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -4825,30 +4837,30 @@
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr"/>
-      <c r="D100" s="6" t="inlineStr"/>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Nuno Cunha (Managing Director)</t>
+        </is>
+      </c>
       <c r="E100" s="6" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr"/>
       <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>reabilita.pt</t>
-        </is>
-      </c>
+      <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>REABILITA</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -4861,10 +4873,14 @@
       <c r="E101" s="6" t="inlineStr"/>
       <c r="F101" s="6" t="inlineStr"/>
       <c r="G101" s="6" t="inlineStr"/>
-      <c r="H101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>reabilita.pt</t>
+        </is>
+      </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -4876,7 +4892,7 @@
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -4892,19 +4908,19 @@
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -4917,26 +4933,22 @@
       <c r="E103" s="6" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr"/>
       <c r="G103" s="6" t="inlineStr"/>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>altadelisboa.com</t>
-        </is>
-      </c>
+      <c r="H103" s="6" t="inlineStr"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>Selicomi Portugal (Victoria Group)</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -4945,34 +4957,26 @@
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr"/>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
-        </is>
-      </c>
+      <c r="D104" s="6" t="inlineStr"/>
       <c r="E104" s="6" t="inlineStr"/>
       <c r="F104" s="6" t="inlineStr"/>
       <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr">
-        <is>
-          <t>shaluinvest.pt</t>
-        </is>
-      </c>
+      <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -4985,130 +4989,122 @@
       <c r="E105" s="6" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr"/>
       <c r="G105" s="6" t="inlineStr"/>
-      <c r="H105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>altadelisboa.com</t>
+        </is>
+      </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>Shalu Investments</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr"/>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
-        </is>
-      </c>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr"/>
       <c r="F106" s="6" t="inlineStr"/>
       <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Grândola/Lagoa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>Emblezart</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>Square Asset Management</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr"/>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+      <c r="D107" s="6" t="inlineStr"/>
+      <c r="E107" s="6" t="inlineStr"/>
       <c r="F107" s="6" t="inlineStr"/>
       <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>squaream.pt</t>
+        </is>
+      </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>Taga Urbanic</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr"/>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+      <c r="D108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr"/>
       <c r="F108" s="6" t="inlineStr"/>
       <c r="G108" s="6" t="inlineStr"/>
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -5119,36 +5115,32 @@
       <c r="C109" s="8" t="inlineStr"/>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Igor Castro (CEO)</t>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
       <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
@@ -5159,36 +5151,32 @@
       <c r="C110" s="8" t="inlineStr"/>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
+          <t>David Faria (CEO e sócio único)</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
       <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -5199,36 +5187,32 @@
       <c r="C111" s="8" t="inlineStr"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+          <t>Carlos Silva Neves (administrador)</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
       <c r="G111" s="6" t="inlineStr"/>
-      <c r="H111" s="6" t="inlineStr">
-        <is>
-          <t>ombria.com</t>
-        </is>
-      </c>
+      <c r="H111" s="6" t="inlineStr"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
@@ -5239,36 +5223,36 @@
       <c r="C112" s="8" t="inlineStr"/>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
+          <t>Igor Castro (CEO)</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
       <c r="G112" s="6" t="inlineStr"/>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>soccal-vaz.com</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -5279,24 +5263,24 @@
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
+          <t>António Ribeiro da Cunha (CEO)</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
       <c r="G113" s="6" t="inlineStr"/>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>mellordc.pt</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
@@ -5308,7 +5292,7 @@
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
@@ -5319,36 +5303,36 @@
       <c r="C114" s="8" t="inlineStr"/>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
       <c r="G114" s="6" t="inlineStr"/>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>ombria.com</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -5359,36 +5343,36 @@
       <c r="C115" s="8" t="inlineStr"/>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
+          <t>António Vaz (fundador e CEO)</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
       <c r="G115" s="6" t="inlineStr"/>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>soccal-vaz.com</t>
         </is>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Algarve Property Shops</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -5397,26 +5381,38 @@
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr"/>
-      <c r="D116" s="6" t="inlineStr"/>
-      <c r="E116" s="6" t="inlineStr"/>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="F116" s="6" t="inlineStr"/>
       <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>solidsentinel.pt</t>
+        </is>
+      </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -5425,26 +5421,38 @@
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr"/>
-      <c r="D117" s="6" t="inlineStr"/>
-      <c r="E117" s="6" t="inlineStr"/>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+        </is>
+      </c>
       <c r="F117" s="6" t="inlineStr"/>
       <c r="G117" s="6" t="inlineStr"/>
-      <c r="H117" s="6" t="inlineStr"/>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>sonaesierra.com</t>
+        </is>
+      </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>nacional</t>
         </is>
       </c>
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
@@ -5455,28 +5463,36 @@
       <c r="C118" s="8" t="inlineStr"/>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr"/>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+        </is>
+      </c>
       <c r="F118" s="6" t="inlineStr"/>
       <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr"/>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
@@ -5485,34 +5501,26 @@
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr"/>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
+      <c r="D119" s="6" t="inlineStr"/>
       <c r="E119" s="6" t="inlineStr"/>
       <c r="F119" s="6" t="inlineStr"/>
       <c r="G119" s="6" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
@@ -5528,19 +5536,19 @@
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
@@ -5549,14 +5557,18 @@
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr"/>
-      <c r="D121" s="6" t="inlineStr"/>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="E121" s="6" t="inlineStr"/>
       <c r="F121" s="6" t="inlineStr"/>
       <c r="G121" s="6" t="inlineStr"/>
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -5568,7 +5580,7 @@
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
@@ -5577,30 +5589,34 @@
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr"/>
-      <c r="D122" s="6" t="inlineStr"/>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="E122" s="6" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr"/>
       <c r="G122" s="6" t="inlineStr"/>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>casasdosotavento.pt</t>
+          <t>baltor.pt</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
@@ -5616,19 +5632,19 @@
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
@@ -5644,19 +5660,19 @@
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
@@ -5671,24 +5687,24 @@
       <c r="G125" s="6" t="inlineStr"/>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>discoverylandco.com</t>
+          <t>casasdosotavento.pt</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
@@ -5704,7 +5720,7 @@
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
@@ -5716,7 +5732,7 @@
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
@@ -5725,30 +5741,26 @@
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr"/>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+      <c r="D127" s="6" t="inlineStr"/>
       <c r="E127" s="6" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr"/>
       <c r="G127" s="6" t="inlineStr"/>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Guarda</t>
         </is>
       </c>
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
@@ -5757,30 +5769,30 @@
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr"/>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
+      <c r="D128" s="6" t="inlineStr"/>
       <c r="E128" s="6" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr"/>
       <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
@@ -5789,34 +5801,26 @@
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr"/>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
-        </is>
-      </c>
+      <c r="D129" s="6" t="inlineStr"/>
       <c r="E129" s="6" t="inlineStr"/>
       <c r="F129" s="6" t="inlineStr"/>
       <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
@@ -5827,7 +5831,7 @@
       <c r="C130" s="8" t="inlineStr"/>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr"/>
@@ -5836,19 +5840,19 @@
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
@@ -5857,26 +5861,30 @@
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr"/>
-      <c r="D131" s="6" t="inlineStr"/>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
+        </is>
+      </c>
       <c r="E131" s="6" t="inlineStr"/>
       <c r="F131" s="6" t="inlineStr"/>
       <c r="G131" s="6" t="inlineStr"/>
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
@@ -5885,26 +5893,34 @@
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr"/>
-      <c r="D132" s="6" t="inlineStr"/>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="E132" s="6" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr"/>
       <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
@@ -5913,14 +5929,18 @@
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr"/>
-      <c r="D133" s="6" t="inlineStr"/>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="E133" s="6" t="inlineStr"/>
       <c r="F133" s="6" t="inlineStr"/>
       <c r="G133" s="6" t="inlineStr"/>
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
@@ -5932,7 +5952,7 @@
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
@@ -5945,14 +5965,10 @@
       <c r="E134" s="6" t="inlineStr"/>
       <c r="F134" s="6" t="inlineStr"/>
       <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
@@ -5964,7 +5980,7 @@
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -5973,34 +5989,26 @@
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr"/>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+      <c r="D135" s="6" t="inlineStr"/>
       <c r="E135" s="6" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr"/>
       <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
@@ -6013,26 +6021,22 @@
       <c r="E136" s="6" t="inlineStr"/>
       <c r="F136" s="6" t="inlineStr"/>
       <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>glowing.pt</t>
-        </is>
-      </c>
+      <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
@@ -6045,22 +6049,26 @@
       <c r="E137" s="6" t="inlineStr"/>
       <c r="F137" s="6" t="inlineStr"/>
       <c r="G137" s="6" t="inlineStr"/>
-      <c r="H137" s="6" t="inlineStr"/>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>genuinoinvestments.com</t>
+        </is>
+      </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -6071,7 +6079,7 @@
       <c r="C138" s="8" t="inlineStr"/>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
@@ -6079,16 +6087,24 @@
       <c r="G138" s="6" t="inlineStr"/>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="I138" s="8" t="inlineStr"/>
-      <c r="J138" s="8" t="inlineStr"/>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>Faro/Loulé</t>
+        </is>
+      </c>
+      <c r="J138" s="8" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
@@ -6097,34 +6113,30 @@
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr"/>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+      <c r="D139" s="6" t="inlineStr"/>
       <c r="E139" s="6" t="inlineStr"/>
       <c r="F139" s="6" t="inlineStr"/>
       <c r="G139" s="6" t="inlineStr"/>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>andrejordangroup.pt</t>
+          <t>glowing.pt</t>
         </is>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -6133,18 +6145,14 @@
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr"/>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
-        </is>
-      </c>
+      <c r="D140" s="6" t="inlineStr"/>
       <c r="E140" s="6" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr"/>
       <c r="G140" s="6" t="inlineStr"/>
       <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
@@ -6156,7 +6164,7 @@
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
@@ -6165,30 +6173,26 @@
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr"/>
-      <c r="D141" s="6" t="inlineStr"/>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
+        </is>
+      </c>
       <c r="E141" s="6" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr"/>
       <c r="G141" s="6" t="inlineStr"/>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
-      <c r="I141" s="8" t="inlineStr">
-        <is>
-          <t>Leiria</t>
-        </is>
-      </c>
-      <c r="J141" s="8" t="inlineStr">
-        <is>
-          <t>Leiria</t>
-        </is>
-      </c>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="inlineStr"/>
+      <c r="J141" s="8" t="inlineStr"/>
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
@@ -6199,7 +6203,7 @@
       <c r="C142" s="8" t="inlineStr"/>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Ioav Blanche (presidente)</t>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr"/>
@@ -6207,24 +6211,24 @@
       <c r="G142" s="6" t="inlineStr"/>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>gruponbportugal.pt</t>
+          <t>andrejordangroup.pt</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
@@ -6235,20 +6239,16 @@
       <c r="C143" s="8" t="inlineStr"/>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
+          <t>Aníbal Cristina (fundador, 1990)</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr"/>
       <c r="F143" s="6" t="inlineStr"/>
       <c r="G143" s="6" t="inlineStr"/>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>pestana.com</t>
-        </is>
-      </c>
+      <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J143" s="8" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
@@ -6275,24 +6275,24 @@
       <c r="G144" s="6" t="inlineStr"/>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -6301,30 +6301,34 @@
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr"/>
-      <c r="D145" s="6" t="inlineStr"/>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="E145" s="6" t="inlineStr"/>
       <c r="F145" s="6" t="inlineStr"/>
       <c r="G145" s="6" t="inlineStr"/>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
@@ -6333,26 +6337,34 @@
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr"/>
-      <c r="D146" s="6" t="inlineStr"/>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="E146" s="6" t="inlineStr"/>
       <c r="F146" s="6" t="inlineStr"/>
       <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>pestana.com</t>
+        </is>
+      </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -6367,24 +6379,24 @@
       <c r="G147" s="6" t="inlineStr"/>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>leparc.pt</t>
+          <t>hillside.pt</t>
         </is>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
@@ -6393,34 +6405,30 @@
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr"/>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
+      <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="6" t="inlineStr"/>
       <c r="F148" s="6" t="inlineStr"/>
       <c r="G148" s="6" t="inlineStr"/>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -6429,18 +6437,14 @@
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr"/>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
+      <c r="D149" s="6" t="inlineStr"/>
       <c r="E149" s="6" t="inlineStr"/>
       <c r="F149" s="6" t="inlineStr"/>
       <c r="G149" s="6" t="inlineStr"/>
       <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="J149" s="8" t="inlineStr">
@@ -6452,7 +6456,7 @@
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -6465,22 +6469,26 @@
       <c r="E150" s="6" t="inlineStr"/>
       <c r="F150" s="6" t="inlineStr"/>
       <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -6491,7 +6499,7 @@
       <c r="C151" s="8" t="inlineStr"/>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Claude Berda (fundador)</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr"/>
@@ -6499,24 +6507,24 @@
       <c r="G151" s="6" t="inlineStr"/>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>maveninvest.pt</t>
+          <t>luxpremium.net</t>
         </is>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
@@ -6525,7 +6533,11 @@
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr"/>
-      <c r="D152" s="6" t="inlineStr"/>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+        </is>
+      </c>
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="6" t="inlineStr"/>
       <c r="G152" s="6" t="inlineStr"/>
@@ -6544,7 +6556,7 @@
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -6553,30 +6565,26 @@
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr"/>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
+      <c r="D153" s="6" t="inlineStr"/>
       <c r="E153" s="6" t="inlineStr"/>
       <c r="F153" s="6" t="inlineStr"/>
       <c r="G153" s="6" t="inlineStr"/>
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Santarém</t>
         </is>
       </c>
     </row>
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
@@ -6585,30 +6593,34 @@
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr"/>
-      <c r="D154" s="6" t="inlineStr"/>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
       <c r="E154" s="6" t="inlineStr"/>
       <c r="F154" s="6" t="inlineStr"/>
       <c r="G154" s="6" t="inlineStr"/>
       <c r="H154" s="6" t="inlineStr">
         <is>
-          <t>oconnormurphy.ie</t>
+          <t>maveninvest.pt</t>
         </is>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -6624,7 +6636,7 @@
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J155" s="8" t="inlineStr">
@@ -6636,7 +6648,7 @@
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -6647,7 +6659,7 @@
       <c r="C156" s="8" t="inlineStr"/>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+          <t>Matan Amitai (co-fundador)</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr"/>
@@ -6656,19 +6668,19 @@
       <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
     </row>
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -6681,22 +6693,26 @@
       <c r="E157" s="6" t="inlineStr"/>
       <c r="F157" s="6" t="inlineStr"/>
       <c r="G157" s="6" t="inlineStr"/>
-      <c r="H157" s="6" t="inlineStr"/>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -6712,19 +6728,19 @@
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
@@ -6735,7 +6751,7 @@
       <c r="C159" s="8" t="inlineStr"/>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr"/>
@@ -6744,19 +6760,19 @@
       <c r="H159" s="6" t="inlineStr"/>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -6765,34 +6781,26 @@
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr"/>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+      <c r="D160" s="6" t="inlineStr"/>
       <c r="E160" s="6" t="inlineStr"/>
       <c r="F160" s="6" t="inlineStr"/>
       <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -6808,19 +6816,19 @@
       <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -6829,30 +6837,30 @@
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr"/>
-      <c r="D162" s="6" t="inlineStr"/>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
       <c r="E162" s="6" t="inlineStr"/>
       <c r="F162" s="6" t="inlineStr"/>
       <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>southshoreinvest.com</t>
-        </is>
-      </c>
+      <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="163" ht="26" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -6861,14 +6869,22 @@
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr"/>
-      <c r="D163" s="6" t="inlineStr"/>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
       <c r="E163" s="6" t="inlineStr"/>
       <c r="F163" s="6" t="inlineStr"/>
       <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>rodriguesevermelho.com</t>
+        </is>
+      </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
@@ -6880,7 +6896,7 @@
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -6893,26 +6909,22 @@
       <c r="E164" s="6" t="inlineStr"/>
       <c r="F164" s="6" t="inlineStr"/>
       <c r="G164" s="6" t="inlineStr"/>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>valentavillas.com</t>
-        </is>
-      </c>
+      <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -6925,10 +6937,14 @@
       <c r="E165" s="6" t="inlineStr"/>
       <c r="F165" s="6" t="inlineStr"/>
       <c r="G165" s="6" t="inlineStr"/>
-      <c r="H165" s="6" t="inlineStr"/>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>southshoreinvest.com</t>
+        </is>
+      </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
@@ -6940,7 +6956,7 @@
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -6949,22 +6965,14 @@
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr"/>
-      <c r="D166" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+      <c r="D166" s="6" t="inlineStr"/>
       <c r="E166" s="6" t="inlineStr"/>
       <c r="F166" s="6" t="inlineStr"/>
       <c r="G166" s="6" t="inlineStr"/>
-      <c r="H166" s="6" t="inlineStr">
-        <is>
-          <t>ugp.ie</t>
-        </is>
-      </c>
+      <c r="H166" s="6" t="inlineStr"/>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
@@ -6976,7 +6984,7 @@
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>Urban Office</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -6991,24 +6999,24 @@
       <c r="G167" s="6" t="inlineStr"/>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>urbanoffice.pt</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
-          <t>Torres Vedras</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="168" ht="26" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -7021,26 +7029,22 @@
       <c r="E168" s="6" t="inlineStr"/>
       <c r="F168" s="6" t="inlineStr"/>
       <c r="G168" s="6" t="inlineStr"/>
-      <c r="H168" s="6" t="inlineStr">
-        <is>
-          <t>valedolobo.com</t>
-        </is>
-      </c>
+      <c r="H168" s="6" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="169" ht="26" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -7049,21 +7053,121 @@
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr"/>
-      <c r="D169" s="6" t="inlineStr"/>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="E169" s="6" t="inlineStr"/>
       <c r="F169" s="6" t="inlineStr"/>
       <c r="G169" s="6" t="inlineStr"/>
       <c r="H169" s="6" t="inlineStr">
         <is>
+          <t>ugp.ie</t>
+        </is>
+      </c>
+      <c r="I169" s="8" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="J169" s="8" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="26" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>Urban Office</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr"/>
+      <c r="D170" s="6" t="inlineStr"/>
+      <c r="E170" s="6" t="inlineStr"/>
+      <c r="F170" s="6" t="inlineStr"/>
+      <c r="G170" s="6" t="inlineStr"/>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>urbanoffice.pt</t>
+        </is>
+      </c>
+      <c r="I170" s="8" t="inlineStr">
+        <is>
+          <t>Torres Vedras</t>
+        </is>
+      </c>
+      <c r="J170" s="8" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="26" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr"/>
+      <c r="D171" s="6" t="inlineStr"/>
+      <c r="E171" s="6" t="inlineStr"/>
+      <c r="F171" s="6" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr"/>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="I171" s="8" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="J171" s="8" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="26" customHeight="1">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr"/>
+      <c r="D172" s="6" t="inlineStr"/>
+      <c r="E172" s="6" t="inlineStr"/>
+      <c r="F172" s="6" t="inlineStr"/>
+      <c r="G172" s="6" t="inlineStr"/>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
           <t>vilagale.com</t>
         </is>
       </c>
-      <c r="I169" s="8" t="inlineStr">
+      <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Golegã</t>
         </is>
       </c>
-      <c r="J169" s="8" t="inlineStr">
+      <c r="J172" s="8" t="inlineStr">
         <is>
           <t>Santarém</t>
         </is>
@@ -7117,19 +7221,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -7170,7 +7274,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3">
@@ -7180,7 +7284,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
@@ -7190,7 +7294,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -7200,7 +7304,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -7230,7 +7334,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">

--- a/Lista_Contactos.xlsx
+++ b/Lista_Contactos.xlsx
@@ -203,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Contactos" displayName="Contactos" ref="A1:J172" headerRowCount="1">
-  <autoFilter ref="A1:J172"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Contactos" displayName="Contactos" ref="A1:J174" headerRowCount="1">
+  <autoFilter ref="A1:J174"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4624,7 +4624,7 @@
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Groundfloor – Premium Investments</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -4633,17 +4633,13 @@
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr"/>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
-        </is>
-      </c>
+      <c r="D94" s="6" t="inlineStr"/>
       <c r="E94" s="6" t="inlineStr"/>
       <c r="F94" s="6" t="inlineStr"/>
       <c r="G94" s="6" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>hines.com</t>
+          <t>theartt.pt</t>
         </is>
       </c>
       <c r="I94" s="8" t="inlineStr">
@@ -4660,7 +4656,7 @@
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -4671,7 +4667,7 @@
       <c r="C95" s="8" t="inlineStr"/>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr"/>
@@ -4679,24 +4675,24 @@
       <c r="G95" s="6" t="inlineStr"/>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>imolote.pt</t>
+          <t>hines.com</t>
         </is>
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -4707,13 +4703,17 @@
       <c r="C96" s="8" t="inlineStr"/>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
       <c r="F96" s="6" t="inlineStr"/>
       <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Porto</t>
@@ -4728,7 +4728,7 @@
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>KKR Imo, S.A.</t>
+          <t>JCKL Portugal – Investimentos Imobiliários</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -4737,11 +4737,7 @@
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
-        </is>
-      </c>
+      <c r="D97" s="6" t="inlineStr"/>
       <c r="E97" s="6" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr"/>
       <c r="G97" s="6" t="inlineStr"/>
@@ -4760,7 +4756,7 @@
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Neptune Developments</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -4769,30 +4765,30 @@
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr"/>
-      <c r="D98" s="6" t="inlineStr"/>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+        </is>
+      </c>
       <c r="E98" s="6" t="inlineStr"/>
       <c r="F98" s="6" t="inlineStr"/>
       <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>neptune-developments.com</t>
-        </is>
-      </c>
+      <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Onyria Group</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -4803,20 +4799,16 @@
       <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr"/>
       <c r="G99" s="6" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>onyriagroup.com</t>
-        </is>
-      </c>
+      <c r="H99" s="6" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
@@ -4828,7 +4820,7 @@
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Neptune Developments</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -4837,30 +4829,30 @@
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr"/>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>Nuno Cunha (Managing Director)</t>
-        </is>
-      </c>
+      <c r="D100" s="6" t="inlineStr"/>
       <c r="E100" s="6" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr"/>
       <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>neptune-developments.com</t>
+        </is>
+      </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>REABILITA</t>
+          <t>Onyria Group</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -4869,18 +4861,22 @@
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr"/>
-      <c r="D101" s="6" t="inlineStr"/>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+        </is>
+      </c>
       <c r="E101" s="6" t="inlineStr"/>
       <c r="F101" s="6" t="inlineStr"/>
       <c r="G101" s="6" t="inlineStr"/>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>reabilita.pt</t>
+          <t>onyriagroup.com</t>
         </is>
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -4892,7 +4888,7 @@
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -4901,26 +4897,30 @@
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr"/>
-      <c r="D102" s="6" t="inlineStr"/>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Nuno Cunha (Managing Director)</t>
+        </is>
+      </c>
       <c r="E102" s="6" t="inlineStr"/>
       <c r="F102" s="6" t="inlineStr"/>
       <c r="G102" s="6" t="inlineStr"/>
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REABILITA</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -4933,22 +4933,26 @@
       <c r="E103" s="6" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr"/>
       <c r="G103" s="6" t="inlineStr"/>
-      <c r="H103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>reabilita.pt</t>
+        </is>
+      </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Selicomi Portugal (Victoria Group)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -4964,7 +4968,7 @@
       <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
@@ -4976,7 +4980,7 @@
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -4989,26 +4993,22 @@
       <c r="E105" s="6" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr"/>
       <c r="G105" s="6" t="inlineStr"/>
-      <c r="H105" s="6" t="inlineStr">
-        <is>
-          <t>altadelisboa.com</t>
-        </is>
-      </c>
+      <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>Selicomi Portugal (Victoria Group)</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -5017,34 +5017,26 @@
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr"/>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
-        </is>
-      </c>
+      <c r="D106" s="6" t="inlineStr"/>
       <c r="E106" s="6" t="inlineStr"/>
       <c r="F106" s="6" t="inlineStr"/>
       <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>shaluinvest.pt</t>
-        </is>
-      </c>
+      <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>Square Asset Management</t>
+          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -5059,7 +5051,7 @@
       <c r="G107" s="6" t="inlineStr"/>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>squaream.pt</t>
+          <t>altadelisboa.com</t>
         </is>
       </c>
       <c r="I107" s="8" t="inlineStr">
@@ -5076,7 +5068,7 @@
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -5085,14 +5077,22 @@
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr"/>
-      <c r="D108" s="6" t="inlineStr"/>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
       <c r="E108" s="6" t="inlineStr"/>
       <c r="F108" s="6" t="inlineStr"/>
       <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
@@ -5104,31 +5104,27 @@
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>Square Asset Management</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr"/>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
-        </is>
-      </c>
+      <c r="D109" s="6" t="inlineStr"/>
+      <c r="E109" s="6" t="inlineStr"/>
       <c r="F109" s="6" t="inlineStr"/>
       <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>squaream.pt</t>
+        </is>
+      </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Grândola/Lagoa</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
@@ -5140,43 +5136,35 @@
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>Emblezart</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Nao</t>
+          <t>Taga Urbanic</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr"/>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+      <c r="D110" s="6" t="inlineStr"/>
+      <c r="E110" s="6" t="inlineStr"/>
       <c r="F110" s="6" t="inlineStr"/>
       <c r="G110" s="6" t="inlineStr"/>
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -5187,12 +5175,12 @@
       <c r="C111" s="8" t="inlineStr"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -5200,7 +5188,7 @@
       <c r="H111" s="6" t="inlineStr"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
@@ -5212,7 +5200,7 @@
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
@@ -5223,36 +5211,32 @@
       <c r="C112" s="8" t="inlineStr"/>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Igor Castro (CEO)</t>
+          <t>David Faria (CEO e sócio único)</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
       <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="6" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="H112" s="6" t="inlineStr"/>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -5263,36 +5247,32 @@
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
+          <t>Carlos Silva Neves (administrador)</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
       <c r="G113" s="6" t="inlineStr"/>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="H113" s="6" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
@@ -5303,36 +5283,36 @@
       <c r="C114" s="8" t="inlineStr"/>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+          <t>Igor Castro (CEO)</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
       <c r="G114" s="6" t="inlineStr"/>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>ombria.com</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -5343,24 +5323,24 @@
       <c r="C115" s="8" t="inlineStr"/>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
+          <t>António Ribeiro da Cunha (CEO)</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
       <c r="G115" s="6" t="inlineStr"/>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>soccal-vaz.com</t>
+          <t>mellordc.pt</t>
         </is>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -5372,7 +5352,7 @@
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -5383,36 +5363,36 @@
       <c r="C116" s="8" t="inlineStr"/>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
       <c r="G116" s="6" t="inlineStr"/>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>ombria.com</t>
         </is>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -5423,36 +5403,36 @@
       <c r="C117" s="8" t="inlineStr"/>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
+          <t>António Vaz (fundador e CEO)</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
       <c r="G117" s="6" t="inlineStr"/>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>soccal-vaz.com</t>
         </is>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
@@ -5463,36 +5443,36 @@
       <c r="C118" s="8" t="inlineStr"/>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
+          <t>Alain Gross (Co-Founder e CEO)</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr"/>
       <c r="G118" s="6" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Algarve Property Shops</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
@@ -5501,26 +5481,38 @@
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr"/>
-      <c r="D119" s="6" t="inlineStr"/>
-      <c r="E119" s="6" t="inlineStr"/>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+        </is>
+      </c>
       <c r="F119" s="6" t="inlineStr"/>
       <c r="G119" s="6" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr"/>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>sonaesierra.com</t>
+        </is>
+      </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>nacional</t>
         </is>
       </c>
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
@@ -5529,26 +5521,38 @@
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr"/>
-      <c r="D120" s="6" t="inlineStr"/>
-      <c r="E120" s="6" t="inlineStr"/>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+        </is>
+      </c>
       <c r="F120" s="6" t="inlineStr"/>
       <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
@@ -5557,18 +5561,14 @@
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr"/>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
+      <c r="D121" s="6" t="inlineStr"/>
       <c r="E121" s="6" t="inlineStr"/>
       <c r="F121" s="6" t="inlineStr"/>
       <c r="G121" s="6" t="inlineStr"/>
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
@@ -5589,22 +5589,14 @@
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr"/>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
+      <c r="D122" s="6" t="inlineStr"/>
       <c r="E122" s="6" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr"/>
       <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
@@ -5616,7 +5608,7 @@
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
@@ -5625,26 +5617,30 @@
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr"/>
-      <c r="D123" s="6" t="inlineStr"/>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="E123" s="6" t="inlineStr"/>
       <c r="F123" s="6" t="inlineStr"/>
       <c r="G123" s="6" t="inlineStr"/>
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
@@ -5653,26 +5649,34 @@
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr"/>
-      <c r="D124" s="6" t="inlineStr"/>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="E124" s="6" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr"/>
       <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
@@ -5685,26 +5689,22 @@
       <c r="E125" s="6" t="inlineStr"/>
       <c r="F125" s="6" t="inlineStr"/>
       <c r="G125" s="6" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
@@ -5720,7 +5720,7 @@
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
@@ -5732,7 +5732,7 @@
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
@@ -5745,22 +5745,26 @@
       <c r="E127" s="6" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr"/>
       <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
@@ -5773,26 +5777,22 @@
       <c r="E128" s="6" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr"/>
       <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
@@ -5808,19 +5808,19 @@
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Guarda</t>
         </is>
       </c>
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
@@ -5829,30 +5829,30 @@
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr"/>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+      <c r="D130" s="6" t="inlineStr"/>
       <c r="E130" s="6" t="inlineStr"/>
       <c r="F130" s="6" t="inlineStr"/>
       <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
@@ -5861,30 +5861,26 @@
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr"/>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
+      <c r="D131" s="6" t="inlineStr"/>
       <c r="E131" s="6" t="inlineStr"/>
       <c r="F131" s="6" t="inlineStr"/>
       <c r="G131" s="6" t="inlineStr"/>
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
@@ -5895,32 +5891,28 @@
       <c r="C132" s="8" t="inlineStr"/>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr"/>
       <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
@@ -5931,7 +5923,7 @@
       <c r="C133" s="8" t="inlineStr"/>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr"/>
@@ -5940,19 +5932,19 @@
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
@@ -5961,26 +5953,34 @@
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr"/>
-      <c r="D134" s="6" t="inlineStr"/>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="E134" s="6" t="inlineStr"/>
       <c r="F134" s="6" t="inlineStr"/>
       <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -5989,26 +5989,30 @@
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr"/>
-      <c r="D135" s="6" t="inlineStr"/>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="E135" s="6" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr"/>
       <c r="G135" s="6" t="inlineStr"/>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
@@ -6024,7 +6028,7 @@
       <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
@@ -6036,7 +6040,7 @@
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
@@ -6049,26 +6053,22 @@
       <c r="E137" s="6" t="inlineStr"/>
       <c r="F137" s="6" t="inlineStr"/>
       <c r="G137" s="6" t="inlineStr"/>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -6077,22 +6077,14 @@
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr"/>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+      <c r="D138" s="6" t="inlineStr"/>
       <c r="E138" s="6" t="inlineStr"/>
       <c r="F138" s="6" t="inlineStr"/>
       <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="H138" s="6" t="inlineStr"/>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr">
@@ -6104,7 +6096,7 @@
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
@@ -6119,24 +6111,24 @@
       <c r="G139" s="6" t="inlineStr"/>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -6145,26 +6137,34 @@
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr"/>
-      <c r="D140" s="6" t="inlineStr"/>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="E140" s="6" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr"/>
       <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr"/>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
@@ -6173,26 +6173,30 @@
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr"/>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+      <c r="D141" s="6" t="inlineStr"/>
       <c r="E141" s="6" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr"/>
       <c r="G141" s="6" t="inlineStr"/>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="I141" s="8" t="inlineStr"/>
-      <c r="J141" s="8" t="inlineStr"/>
+          <t>glowing.pt</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="J141" s="8" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
@@ -6201,34 +6205,26 @@
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr"/>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+      <c r="D142" s="6" t="inlineStr"/>
       <c r="E142" s="6" t="inlineStr"/>
       <c r="F142" s="6" t="inlineStr"/>
       <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
+      <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
@@ -6239,28 +6235,24 @@
       <c r="C143" s="8" t="inlineStr"/>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr"/>
       <c r="F143" s="6" t="inlineStr"/>
       <c r="G143" s="6" t="inlineStr"/>
-      <c r="H143" s="6" t="inlineStr"/>
-      <c r="I143" s="8" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="J143" s="8" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="inlineStr"/>
+      <c r="J143" s="8" t="inlineStr"/>
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
@@ -6269,30 +6261,34 @@
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr"/>
-      <c r="D144" s="6" t="inlineStr"/>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
       <c r="E144" s="6" t="inlineStr"/>
       <c r="F144" s="6" t="inlineStr"/>
       <c r="G144" s="6" t="inlineStr"/>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>grupomaisempresas.pt</t>
+          <t>andrejordangroup.pt</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -6303,32 +6299,28 @@
       <c r="C145" s="8" t="inlineStr"/>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>Ioav Blanche (presidente)</t>
+          <t>Aníbal Cristina (fundador, 1990)</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr"/>
       <c r="F145" s="6" t="inlineStr"/>
       <c r="G145" s="6" t="inlineStr"/>
-      <c r="H145" s="6" t="inlineStr">
-        <is>
-          <t>gruponbportugal.pt</t>
-        </is>
-      </c>
+      <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
@@ -6337,34 +6329,30 @@
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr"/>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
-        </is>
-      </c>
+      <c r="D146" s="6" t="inlineStr"/>
       <c r="E146" s="6" t="inlineStr"/>
       <c r="F146" s="6" t="inlineStr"/>
       <c r="G146" s="6" t="inlineStr"/>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -6373,18 +6361,22 @@
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr"/>
-      <c r="D147" s="6" t="inlineStr"/>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="E147" s="6" t="inlineStr"/>
       <c r="F147" s="6" t="inlineStr"/>
       <c r="G147" s="6" t="inlineStr"/>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="J147" s="8" t="inlineStr">
@@ -6396,7 +6388,7 @@
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
@@ -6405,30 +6397,34 @@
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr"/>
-      <c r="D148" s="6" t="inlineStr"/>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="E148" s="6" t="inlineStr"/>
       <c r="F148" s="6" t="inlineStr"/>
       <c r="G148" s="6" t="inlineStr"/>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -6441,22 +6437,26 @@
       <c r="E149" s="6" t="inlineStr"/>
       <c r="F149" s="6" t="inlineStr"/>
       <c r="G149" s="6" t="inlineStr"/>
-      <c r="H149" s="6" t="inlineStr"/>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>hillside.pt</t>
+        </is>
+      </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -6471,12 +6471,12 @@
       <c r="G150" s="6" t="inlineStr"/>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>leparc.pt</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
@@ -6488,7 +6488,7 @@
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -6497,34 +6497,26 @@
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr"/>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
+      <c r="D151" s="6" t="inlineStr"/>
       <c r="E151" s="6" t="inlineStr"/>
       <c r="F151" s="6" t="inlineStr"/>
       <c r="G151" s="6" t="inlineStr"/>
-      <c r="H151" s="6" t="inlineStr">
-        <is>
-          <t>luxpremium.net</t>
-        </is>
-      </c>
+      <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
@@ -6533,18 +6525,18 @@
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr"/>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
+      <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="6" t="inlineStr"/>
       <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="6" t="inlineStr"/>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr">
@@ -6556,7 +6548,7 @@
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -6565,26 +6557,34 @@
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr"/>
-      <c r="D153" s="6" t="inlineStr"/>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="E153" s="6" t="inlineStr"/>
       <c r="F153" s="6" t="inlineStr"/>
       <c r="G153" s="6" t="inlineStr"/>
-      <c r="H153" s="6" t="inlineStr"/>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
@@ -6595,32 +6595,28 @@
       <c r="C154" s="8" t="inlineStr"/>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr"/>
       <c r="F154" s="6" t="inlineStr"/>
       <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="H154" s="6" t="inlineStr"/>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -6636,19 +6632,19 @@
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Santarém</t>
         </is>
       </c>
     </row>
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -6659,28 +6655,32 @@
       <c r="C156" s="8" t="inlineStr"/>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
+          <t>Yehonatan Gourvitch (CEO)</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr"/>
       <c r="F156" s="6" t="inlineStr"/>
       <c r="G156" s="6" t="inlineStr"/>
-      <c r="H156" s="6" t="inlineStr"/>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -6693,14 +6693,10 @@
       <c r="E157" s="6" t="inlineStr"/>
       <c r="F157" s="6" t="inlineStr"/>
       <c r="G157" s="6" t="inlineStr"/>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="J157" s="8" t="inlineStr">
@@ -6712,7 +6708,7 @@
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -6721,26 +6717,30 @@
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr"/>
-      <c r="D158" s="6" t="inlineStr"/>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
       <c r="E158" s="6" t="inlineStr"/>
       <c r="F158" s="6" t="inlineStr"/>
       <c r="G158" s="6" t="inlineStr"/>
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
@@ -6749,30 +6749,30 @@
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr"/>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
+      <c r="D159" s="6" t="inlineStr"/>
       <c r="E159" s="6" t="inlineStr"/>
       <c r="F159" s="6" t="inlineStr"/>
       <c r="G159" s="6" t="inlineStr"/>
-      <c r="H159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -6788,19 +6788,19 @@
       <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -6809,14 +6809,18 @@
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr"/>
-      <c r="D161" s="6" t="inlineStr"/>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="E161" s="6" t="inlineStr"/>
       <c r="F161" s="6" t="inlineStr"/>
       <c r="G161" s="6" t="inlineStr"/>
       <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="J161" s="8" t="inlineStr">
@@ -6828,7 +6832,7 @@
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -6837,30 +6841,26 @@
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr"/>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+      <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="6" t="inlineStr"/>
       <c r="F162" s="6" t="inlineStr"/>
       <c r="G162" s="6" t="inlineStr"/>
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="163" ht="26" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -6869,34 +6869,26 @@
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr"/>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+      <c r="D163" s="6" t="inlineStr"/>
       <c r="E163" s="6" t="inlineStr"/>
       <c r="F163" s="6" t="inlineStr"/>
       <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="H163" s="6" t="inlineStr"/>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -6905,26 +6897,30 @@
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr"/>
-      <c r="D164" s="6" t="inlineStr"/>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
       <c r="E164" s="6" t="inlineStr"/>
       <c r="F164" s="6" t="inlineStr"/>
       <c r="G164" s="6" t="inlineStr"/>
       <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Porto</t>
         </is>
       </c>
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -6933,30 +6929,34 @@
         </is>
       </c>
       <c r="C165" s="8" t="inlineStr"/>
-      <c r="D165" s="6" t="inlineStr"/>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
       <c r="E165" s="6" t="inlineStr"/>
       <c r="F165" s="6" t="inlineStr"/>
       <c r="G165" s="6" t="inlineStr"/>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>southshoreinvest.com</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -6972,19 +6972,19 @@
       <c r="H166" s="6" t="inlineStr"/>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
     </row>
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -6999,24 +6999,24 @@
       <c r="G167" s="6" t="inlineStr"/>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>valentavillas.com</t>
+          <t>southshoreinvest.com</t>
         </is>
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="168" ht="26" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -7032,19 +7032,19 @@
       <c r="H168" s="6" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
     <row r="169" ht="26" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -7053,34 +7053,30 @@
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr"/>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+      <c r="D169" s="6" t="inlineStr"/>
       <c r="E169" s="6" t="inlineStr"/>
       <c r="F169" s="6" t="inlineStr"/>
       <c r="G169" s="6" t="inlineStr"/>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>ugp.ie</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
     </row>
     <row r="170" ht="26" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>Urban Office</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
@@ -7093,26 +7089,22 @@
       <c r="E170" s="6" t="inlineStr"/>
       <c r="F170" s="6" t="inlineStr"/>
       <c r="G170" s="6" t="inlineStr"/>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>urbanoffice.pt</t>
-        </is>
-      </c>
+      <c r="H170" s="6" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>Torres Vedras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
     </row>
     <row r="171" ht="26" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
@@ -7121,18 +7113,22 @@
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr"/>
-      <c r="D171" s="6" t="inlineStr"/>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="E171" s="6" t="inlineStr"/>
       <c r="F171" s="6" t="inlineStr"/>
       <c r="G171" s="6" t="inlineStr"/>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>valedolobo.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="J171" s="8" t="inlineStr">
@@ -7144,7 +7140,7 @@
     <row r="172" ht="26" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Office</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
@@ -7159,15 +7155,79 @@
       <c r="G172" s="6" t="inlineStr"/>
       <c r="H172" s="6" t="inlineStr">
         <is>
+          <t>urbanoffice.pt</t>
+        </is>
+      </c>
+      <c r="I172" s="8" t="inlineStr">
+        <is>
+          <t>Torres Vedras</t>
+        </is>
+      </c>
+      <c r="J172" s="8" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="26" customHeight="1">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr"/>
+      <c r="D173" s="6" t="inlineStr"/>
+      <c r="E173" s="6" t="inlineStr"/>
+      <c r="F173" s="6" t="inlineStr"/>
+      <c r="G173" s="6" t="inlineStr"/>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="I173" s="8" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="J173" s="8" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="26" customHeight="1">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr"/>
+      <c r="D174" s="6" t="inlineStr"/>
+      <c r="E174" s="6" t="inlineStr"/>
+      <c r="F174" s="6" t="inlineStr"/>
+      <c r="G174" s="6" t="inlineStr"/>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
           <t>vilagale.com</t>
         </is>
       </c>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="I174" s="8" t="inlineStr">
         <is>
           <t>Golegã</t>
         </is>
       </c>
-      <c r="J172" s="8" t="inlineStr">
+      <c r="J174" s="8" t="inlineStr">
         <is>
           <t>Santarém</t>
         </is>
@@ -7224,16 +7284,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -7274,7 +7334,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
@@ -7294,7 +7354,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -7334,7 +7394,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
